--- a/Project_01 - Automation_Exercise/Automation Exercise - Bug Report.xlsx
+++ b/Project_01 - Automation_Exercise/Automation Exercise - Bug Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarence\OneDrive\Desktop\Automation Exercise QA Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarence\OneDrive\Desktop\Manul Testing Projects\Automation Exercise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C87677E-F75D-4BC6-81BC-BF353828A273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B239C73-19E0-4129-B171-F2A192887619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C04DD6B-39AA-404A-8B29-B27D176F847F}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>AE-001</t>
   </si>
   <si>
-    <t>Product "Top and Short" incorrectly displayed in the "Kids -&gt; Dress" sub-category</t>
-  </si>
-  <si>
     <t>1. Open the website https://automationexercise.com/
 2. Click the “Product“ in the header navigation bar
 3. In the “Category sidebar“ locate “KIDS“ category
@@ -105,9 +102,6 @@
     <t>AE-002</t>
   </si>
   <si>
-    <t>Misaligned product grid due to inconsistent image aspect ratios/dimensions</t>
-  </si>
-  <si>
     <t>1. Open the website https://automationexercise.com/ 
 2. Click “Proucts“ in the header navigation bar
 3. Scroll down the product listing page 
@@ -121,6 +115,12 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Product Results Page -&gt; Product "Top and Short" incorrectly displayed in the "Kids -&gt; Dress" sub-category</t>
+  </si>
+  <si>
+    <t>Product List Page -&gt; Misaligned product grid due to inconsistent image aspect ratios/dimensions</t>
   </si>
 </sst>
 </file>
@@ -616,10 +616,10 @@
         <v>10</v>
       </c>
       <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -627,45 +627,45 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
